--- a/artfynd/A 13526-2025 artfynd.xlsx
+++ b/artfynd/A 13526-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83315</v>
+        <v>83314</v>
       </c>
       <c r="B2" t="n">
-        <v>94120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633551.1082617717</v>
+        <v>633551</v>
       </c>
       <c r="R2" t="n">
-        <v>6665106.85633544</v>
+        <v>6665092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2003-08-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2003-08-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Riklig på murken tallåga</t>
+          <t>Sparsam på murken tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +772,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -807,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83314</v>
+        <v>83315</v>
       </c>
       <c r="B3" t="n">
-        <v>94120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633551.1527631351</v>
+        <v>633551</v>
       </c>
       <c r="R3" t="n">
-        <v>6665091.883954398</v>
+        <v>6665107</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,24 +864,14 @@
           <t>2003-08-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2003-08-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sparsam på murken tallåga</t>
+          <t>Riklig på murken tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,6 +888,7 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
